--- a/Thesis_TSSP_NEW_M2_Results_1_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_1_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.4900 sec</t>
+          <t>1.4350 sec</t>
         </is>
       </c>
     </row>

--- a/Thesis_TSSP_NEW_M2_Results_1_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_1_Scenarios.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 08:04</t>
+          <t>4/5/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -500,17 +500,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 14:38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:01</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
     </row>
@@ -547,17 +547,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 12:09</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -579,27 +579,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 14:58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 14:27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 13:21</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 12:03</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 10:10</t>
+          <t>4/5/2026 10:47</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -653,17 +653,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:42</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
     </row>
@@ -685,32 +685,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 14:59</t>
+          <t>4/5/2026 07:33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 14:52</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:17</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
     </row>
@@ -722,32 +722,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>4/5/2026 13:24</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Transport Cart 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>4/5/2026 15:09</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Transport Cart 3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4/5/2026 15:09</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:40</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
     </row>
@@ -764,27 +764,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 13:58</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:03</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:34</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 09:52</t>
+          <t>4/5/2026 14:28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:00</t>
+          <t>4/5/2026 08:05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:18</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 12:30</t>
+          <t>4/5/2026 13:45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
     </row>
@@ -907,22 +907,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 14:18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
     </row>
@@ -944,32 +944,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 12:30</t>
+          <t>4/5/2026 10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 06:17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:33</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 14:56</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:52</t>
+          <t>4/5/2026 07:59</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1023,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 15:01</t>
+          <t>4/5/2026 13:20</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 15:07</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
     </row>
@@ -1055,22 +1055,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 14:50</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 15:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 13:50</t>
+          <t>4/5/2026 13:44</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:55</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
     </row>
@@ -1171,27 +1171,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 12:36</t>
+          <t>4/5/2026 13:31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1218,17 +1218,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 11:03</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>463.00 min</t>
+          <t>468.00 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.10 min</t>
+          <t>40.57 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22.00 min</t>
+          <t>27.00 min</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.4350 sec</t>
+          <t>1.3700 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.2048 %</t>
+          <t>0.0000 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>38.10 min | 82.00 min</t>
+          <t>40.57 min | 82.00 min</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8.1</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="32">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12.16</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="33">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.18</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="34">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8.1</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="35">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.87</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="36">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="37">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.38</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="38">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>41.04</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="39">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12.31</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="40">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32.83</v>
+        <v>28.42</v>
       </c>
     </row>
   </sheetData>
@@ -1724,48 +1724,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 07:54</t>
+          <t>4/5/2026 08:04</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 08:11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 08:13</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4/5/2026 08:04</t>
+          <t>4/5/2026 08:23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4/5/2026 08:31</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1904,48 +1904,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 13:08</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4/5/2026 13:10</t>
+          <t>4/5/2026 13:14</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 13:21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4/5/2026 13:43</t>
+          <t>4/5/2026 13:48</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -1964,48 +1964,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>4/5/2026 09:08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:09</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:09</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>4/5/2026 09:14</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:15</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:22</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:24</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:29</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:30</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>22</v>
-      </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2037,35 +2037,35 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:42</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="N7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2097,35 +2097,35 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:05</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:17</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:40</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2170,22 +2170,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:40</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:07</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2230,22 +2230,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2264,48 +2264,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:45</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:34</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:49</t>
+          <t>4/5/2026 08:06</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:38</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -2384,48 +2384,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -2444,48 +2444,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2517,35 +2517,35 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:33</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:35</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -2590,22 +2590,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:52</t>
+          <t>4/5/2026 07:59</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 08:03</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2624,25 +2624,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2650,22 +2650,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -2684,48 +2684,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N18" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2744,48 +2744,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:36</t>
+          <t>4/5/2026 12:26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4/5/2026 13:26</t>
+          <t>4/5/2026 13:13</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2804,48 +2804,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:11</t>
+          <t>4/5/2026 10:21</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:11</t>
+          <t>4/5/2026 10:28</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -2877,35 +2877,35 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2924,48 +2924,48 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>4/5/2026 08:56</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:02</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:02</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:04</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>4/5/2026 09:05</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:11</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:16</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:18</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:26</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="N22" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
